--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260910.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>289,537,616</t>
+          <t>69,599,320</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>69,599,320</t>
+          <t>289,537,616</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>66,339,439</t>
+          <t>139,079,871</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>139,079,871</t>
+          <t>66,339,439</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>107,143,310</t>
+          <t>25,280,032</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>146,701,085</t>
+          <t>107,143,310</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>25,280,032</t>
+          <t>146,701,085</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
